--- a/data/trans_orig/P64D1_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P64D1_R-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>46003</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17053</t>
+          <t>31763</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45470</t>
+          <t>62324</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16979</t>
+          <t>20065</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38177</t>
+          <t>42780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>46,99%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>56029</t>
+          <t>76604</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>56058</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74262</t>
+          <t>97996</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>49,85%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60730</t>
+          <t>58818</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45147</t>
+          <t>42497</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73564</t>
+          <t>73058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>55096</t>
+          <t>61141</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43061</t>
+          <t>48963</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>64259</t>
+          <t>71678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>53,01%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,1%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115826</t>
+          <t>119960</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>97593</t>
+          <t>98568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131859</t>
+          <t>140506</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>71,48%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>90617</t>
+          <t>104821</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>81238</t>
+          <t>91743</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>171855</t>
+          <t>196564</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>73969</t>
+          <t>84624</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58556</t>
+          <t>65255</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>97083</t>
+          <t>108020</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>169975</t>
+          <t>118871</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>118016</t>
+          <t>101269</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>260386</t>
+          <t>135810</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>43,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>243945</t>
+          <t>203496</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>184007</t>
+          <t>173084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>381669</t>
+          <t>229620</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>32,29%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>276374</t>
+          <t>311296</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>253260</t>
+          <t>287900</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>291787</t>
+          <t>330665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>78,89%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,72%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>179745</t>
+          <t>196248</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89334</t>
+          <t>179309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>231704</t>
+          <t>213850</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>51,4%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>56,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>456118</t>
+          <t>507544</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>318394</t>
+          <t>481420</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>516056</t>
+          <t>537956</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,15%</t>
+          <t>71,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,72%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>350343</t>
+          <t>395920</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>315119</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>315119</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>349720</t>
+          <t>315119</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>700063</t>
+          <t>711040</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>700063</t>
+          <t>711040</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>700063</t>
+          <t>711040</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>100673</t>
+          <t>123032</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84375</t>
+          <t>102983</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118271</t>
+          <t>144973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>122608</t>
+          <t>143447</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109000</t>
+          <t>128029</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>136965</t>
+          <t>159717</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>32,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>40,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>223282</t>
+          <t>266479</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>201943</t>
+          <t>241276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246386</t>
+          <t>293104</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>28,55%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,3%</t>
+          <t>31,4%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>361293</t>
+          <t>413464</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>343695</t>
+          <t>391523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>377591</t>
+          <t>433513</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,74%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>228598</t>
+          <t>253552</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214241</t>
+          <t>237282</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>242206</t>
+          <t>268970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>63,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>59,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>67,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>589890</t>
+          <t>667016</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>566786</t>
+          <t>640391</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>611229</t>
+          <t>692219</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>72,54%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,7%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>461966</t>
+          <t>536496</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>461966</t>
+          <t>536496</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>461966</t>
+          <t>536496</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>396999</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>396999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>351206</t>
+          <t>396999</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>813172</t>
+          <t>933495</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>813172</t>
+          <t>933495</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>813172</t>
+          <t>933495</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>110931</t>
+          <t>124578</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>41597</t>
+          <t>104984</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>171545</t>
+          <t>144642</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>150686</t>
+          <t>159841</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>118633</t>
+          <t>144447</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>172962</t>
+          <t>176880</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>33,27%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,19%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>261617</t>
+          <t>284419</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>127216</t>
+          <t>259353</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>340470</t>
+          <t>312271</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>31,27%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>634151</t>
+          <t>418972</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>573537</t>
+          <t>398908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>703485</t>
+          <t>438566</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>73,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>302198</t>
+          <t>295144</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>279922</t>
+          <t>278105</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>334251</t>
+          <t>310538</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>61,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>68,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>936349</t>
+          <t>714116</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>857496</t>
+          <t>686264</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1070750</t>
+          <t>739182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>74,03%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>745082</t>
+          <t>543550</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>745082</t>
+          <t>543550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>745082</t>
+          <t>543550</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>452884</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>452884</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>452884</t>
+          <t>454985</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1197966</t>
+          <t>998535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1197966</t>
+          <t>998535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1197966</t>
+          <t>998535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>82255</t>
+          <t>87515</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69510</t>
+          <t>72800</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97538</t>
+          <t>103390</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>26,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>96039</t>
+          <t>106566</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>84385</t>
+          <t>95180</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>106090</t>
+          <t>118974</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>46,14%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>40,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>178293</t>
+          <t>194082</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>160087</t>
+          <t>173712</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196402</t>
+          <t>214905</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>34,65%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,56%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>38,72%</t>
+          <t>38,37%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>216883</t>
+          <t>239891</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>201600</t>
+          <t>224016</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>229628</t>
+          <t>254606</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>77,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>112097</t>
+          <t>126166</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>102046</t>
+          <t>113758</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>123751</t>
+          <t>137552</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>59,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>328981</t>
+          <t>366056</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310872</t>
+          <t>345233</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>347187</t>
+          <t>386426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>64,85%</t>
+          <t>65,35%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,44%</t>
+          <t>68,99%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>299138</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208136</t>
+          <t>232732</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>507274</t>
+          <t>560138</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9417</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>6204</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>14282</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,14%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10806</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>7908</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13466</t>
+          <t>14229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>60,88%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>20224</t>
+          <t>21636</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>15846</t>
+          <t>16037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24385</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>70,29%</t>
+          <t>67,76%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4212</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>12314</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>44,42%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>8481</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4285</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>11812</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>39,12%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,14%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>17250</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>10309</t>
+          <t>12537</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18848</t>
+          <t>22849</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>16943</t>
+          <t>19166</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>17751</t>
+          <t>19720</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>34694</t>
+          <t>38886</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,7 +2783,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>852</t>
+          <t>930</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>746</t>
+          <t>887</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>46,68%</t>
+          <t>48,81%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1598</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>407985</t>
+          <t>477078</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>274125</t>
+          <t>435206</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>478461</t>
+          <t>519577</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>516941</t>
+          <t>537411</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>709865</t>
+          <t>603879</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>984242</t>
+          <t>1047645</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>808557</t>
+          <t>992323</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1142099</t>
+          <t>1098725</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1557701</t>
+          <t>1452097</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1487225</t>
+          <t>1409598</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1691561</t>
+          <t>1493969</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>884679</t>
+          <t>940731</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>751070</t>
+          <t>907419</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>943994</t>
+          <t>973887</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2442380</t>
+          <t>2392828</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2284523</t>
+          <t>2341748</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2618065</t>
+          <t>2448150</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
